--- a/WorkBot/refactor-experimental/data/order_archive/Sysco/Sysco_Syracuse_20251223.xlsx
+++ b/WorkBot/refactor-experimental/data/order_archive/Sysco/Sysco_Syracuse_20251223.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,13 +455,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>25.01</v>
       </c>
       <c r="E2" t="n">
-        <v>25.01</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="3">
@@ -651,6 +651,48 @@
       </c>
       <c r="E11" t="n">
         <v>47.78</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7468507</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gatorade Lemon Lime</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7468531</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gatorade Cool Blue</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>29.4</v>
       </c>
     </row>
   </sheetData>
